--- a/GORAT circuit diagram/GoRATv0.2.xlsx
+++ b/GORAT circuit diagram/GoRATv0.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/nh22239_bristol_ac_uk/Documents/Documents/GitHub/GORAT-guitar-pedal/GORAT circuit diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47C4037F-8D28-4DF1-94F0-25874F942EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{47C4037F-8D28-4DF1-94F0-25874F942EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D724ABA-583D-4AD1-B578-83AF16D9700B}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{21146C73-3D44-4431-9454-946EEF1445F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{21146C73-3D44-4431-9454-946EEF1445F6}"/>
   </bookViews>
   <sheets>
     <sheet name="GoRATv0.2" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <calcPr calcId="191029" refMode="R1C1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="185">
   <si>
     <t>Reference</t>
   </si>
@@ -2628,6 +2627,9 @@
       <c r="J35" t="s">
         <v>87</v>
       </c>
+      <c r="K35" t="s">
+        <v>154</v>
+      </c>
       <c r="L35" t="s">
         <v>151</v>
       </c>
@@ -2657,6 +2659,9 @@
       <c r="J36" t="s">
         <v>90</v>
       </c>
+      <c r="K36" t="s">
+        <v>154</v>
+      </c>
       <c r="L36" t="s">
         <v>159</v>
       </c>
@@ -2720,6 +2725,9 @@
       <c r="J39" t="s">
         <v>94</v>
       </c>
+      <c r="K39" t="s">
+        <v>154</v>
+      </c>
       <c r="L39" t="s">
         <v>145</v>
       </c>
@@ -2749,6 +2757,9 @@
       <c r="J40" t="s">
         <v>94</v>
       </c>
+      <c r="K40" t="s">
+        <v>154</v>
+      </c>
       <c r="L40" t="s">
         <v>146</v>
       </c>
@@ -2774,6 +2785,9 @@
       </c>
       <c r="E41">
         <v>5</v>
+      </c>
+      <c r="K41" t="s">
+        <v>154</v>
       </c>
       <c r="L41" t="s">
         <v>184</v>
